--- a/Stock_OneClick/history/scan_result_20260601_131535.xlsx
+++ b/Stock_OneClick/history/scan_result_20260601_131535.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q120"/>
+  <dimension ref="A1:Q119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -661,24 +661,6 @@
       <c r="J3" t="n">
         <v>185.67</v>
       </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
-      <c r="L3" t="n">
-        <v/>
-      </c>
-      <c r="M3" t="n">
-        <v/>
-      </c>
-      <c r="N3" t="n">
-        <v/>
-      </c>
-      <c r="O3" t="n">
-        <v/>
-      </c>
-      <c r="P3" t="n">
-        <v/>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-06-01; 相对D0=2.30%; 本次触发=2026-06-01(正式买入 | 预警买入); 历史重复2次; 重复日期=2026-05-27, 2026-06-01</t>
@@ -730,24 +712,6 @@
       <c r="J4" t="n">
         <v>136.62</v>
       </c>
-      <c r="K4" t="n">
-        <v/>
-      </c>
-      <c r="L4" t="n">
-        <v/>
-      </c>
-      <c r="M4" t="n">
-        <v/>
-      </c>
-      <c r="N4" t="n">
-        <v/>
-      </c>
-      <c r="O4" t="n">
-        <v/>
-      </c>
-      <c r="P4" t="n">
-        <v/>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-06-01; 相对D0=-3.26%; 本次触发=2026-06-01(预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -799,27 +763,15 @@
       <c r="J5" s="5" t="n">
         <v>189</v>
       </c>
-      <c r="K5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
       <c r="Q5" s="5" t="inlineStr">
         <is>
-          <t>D0=179.36; 最新=2026-06-01; 相对D0=5.37%; 本次触发=2026-06-01(正式买入 | 第一买入点 | 预警买入); 历史重复3次; 重复日期=2026-05-26, 2026-05-28, 2026-06-01</t>
+          <t>D0=179.36; 最新=2026-06-01; 相对D0=5.37%; 本次触发=2026-06-01(正式买入 | 第一观察点 | 预警买入); 历史重复3次; 重复日期=2026-05-26, 2026-05-28, 2026-06-01</t>
         </is>
       </c>
     </row>
@@ -868,24 +820,6 @@
       <c r="J6" t="n">
         <v>72.75</v>
       </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
-      <c r="L6" t="n">
-        <v/>
-      </c>
-      <c r="M6" t="n">
-        <v/>
-      </c>
-      <c r="N6" t="n">
-        <v/>
-      </c>
-      <c r="O6" t="n">
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v/>
-      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>D0=73.46; 最新=2026-06-01; 相对D0=-0.97%; 本次触发=2026-06-01(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -937,24 +871,12 @@
       <c r="J7" s="5" t="n">
         <v>66.89</v>
       </c>
-      <c r="K7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P7" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
       <c r="Q7" s="5" t="inlineStr">
         <is>
           <t>D0=68.70; 最新=2026-06-01; 相对D0=-2.63%; 本次触发=2026-06-01(预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -1006,24 +928,12 @@
       <c r="J8" s="5" t="n">
         <v>17.62</v>
       </c>
-      <c r="K8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P8" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
       <c r="Q8" s="5" t="inlineStr">
         <is>
           <t>D0=18.40; 最新=2026-06-01; 相对D0=-4.24%; 本次触发=2026-06-01(预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -1075,24 +985,6 @@
       <c r="J9" t="n">
         <v>323.39</v>
       </c>
-      <c r="K9" t="n">
-        <v/>
-      </c>
-      <c r="L9" t="n">
-        <v/>
-      </c>
-      <c r="M9" t="n">
-        <v/>
-      </c>
-      <c r="N9" t="n">
-        <v/>
-      </c>
-      <c r="O9" t="n">
-        <v/>
-      </c>
-      <c r="P9" t="n">
-        <v/>
-      </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>D0=323.91; 最新=2026-06-01; 相对D0=-0.16%; 本次触发=2026-06-01(预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -1144,24 +1036,12 @@
       <c r="J10" s="5" t="n">
         <v>224.36</v>
       </c>
-      <c r="K10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P10" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+      <c r="P10" s="5" t="n"/>
       <c r="Q10" s="5" t="inlineStr">
         <is>
           <t>D0=211.14; 最新=2026-06-01; 相对D0=6.26%; 本次触发=2026-06-01(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -1213,24 +1093,6 @@
       <c r="J11" t="n">
         <v>14.7</v>
       </c>
-      <c r="K11" t="n">
-        <v/>
-      </c>
-      <c r="L11" t="n">
-        <v/>
-      </c>
-      <c r="M11" t="n">
-        <v/>
-      </c>
-      <c r="N11" t="n">
-        <v/>
-      </c>
-      <c r="O11" t="n">
-        <v/>
-      </c>
-      <c r="P11" t="n">
-        <v/>
-      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>D0=14.70; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -1282,24 +1144,6 @@
       <c r="J12" t="n">
         <v>320.41</v>
       </c>
-      <c r="K12" t="n">
-        <v/>
-      </c>
-      <c r="L12" t="n">
-        <v/>
-      </c>
-      <c r="M12" t="n">
-        <v/>
-      </c>
-      <c r="N12" t="n">
-        <v/>
-      </c>
-      <c r="O12" t="n">
-        <v/>
-      </c>
-      <c r="P12" t="n">
-        <v/>
-      </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>D0=320.41; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -1351,24 +1195,6 @@
       <c r="J13" t="n">
         <v>185.83</v>
       </c>
-      <c r="K13" t="n">
-        <v/>
-      </c>
-      <c r="L13" t="n">
-        <v/>
-      </c>
-      <c r="M13" t="n">
-        <v/>
-      </c>
-      <c r="N13" t="n">
-        <v/>
-      </c>
-      <c r="O13" t="n">
-        <v/>
-      </c>
-      <c r="P13" t="n">
-        <v/>
-      </c>
       <c r="Q13" t="inlineStr">
         <is>
           <t>D0=185.83; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -1420,24 +1246,6 @@
       <c r="J14" t="n">
         <v>8.970000000000001</v>
       </c>
-      <c r="K14" t="n">
-        <v/>
-      </c>
-      <c r="L14" t="n">
-        <v/>
-      </c>
-      <c r="M14" t="n">
-        <v/>
-      </c>
-      <c r="N14" t="n">
-        <v/>
-      </c>
-      <c r="O14" t="n">
-        <v/>
-      </c>
-      <c r="P14" t="n">
-        <v/>
-      </c>
       <c r="Q14" t="inlineStr">
         <is>
           <t>D0=8.97; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -1489,24 +1297,6 @@
       <c r="J15" t="n">
         <v>27.15</v>
       </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>D0=27.15; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -1558,24 +1348,6 @@
       <c r="J16" t="n">
         <v>50.55</v>
       </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>D0=50.55; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -1627,24 +1399,6 @@
       <c r="J17" t="n">
         <v>905</v>
       </c>
-      <c r="K17" t="n">
-        <v/>
-      </c>
-      <c r="L17" t="n">
-        <v/>
-      </c>
-      <c r="M17" t="n">
-        <v/>
-      </c>
-      <c r="N17" t="n">
-        <v/>
-      </c>
-      <c r="O17" t="n">
-        <v/>
-      </c>
-      <c r="P17" t="n">
-        <v/>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>D0=905.00; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -1696,24 +1450,6 @@
       <c r="J18" t="n">
         <v>11.02</v>
       </c>
-      <c r="K18" t="n">
-        <v/>
-      </c>
-      <c r="L18" t="n">
-        <v/>
-      </c>
-      <c r="M18" t="n">
-        <v/>
-      </c>
-      <c r="N18" t="n">
-        <v/>
-      </c>
-      <c r="O18" t="n">
-        <v/>
-      </c>
-      <c r="P18" t="n">
-        <v/>
-      </c>
       <c r="Q18" t="inlineStr">
         <is>
           <t>D0=11.02; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -1765,24 +1501,6 @@
       <c r="J19" t="n">
         <v>69.56999999999999</v>
       </c>
-      <c r="K19" t="n">
-        <v/>
-      </c>
-      <c r="L19" t="n">
-        <v/>
-      </c>
-      <c r="M19" t="n">
-        <v/>
-      </c>
-      <c r="N19" t="n">
-        <v/>
-      </c>
-      <c r="O19" t="n">
-        <v/>
-      </c>
-      <c r="P19" t="n">
-        <v/>
-      </c>
       <c r="Q19" t="inlineStr">
         <is>
           <t>D0=69.57; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -1834,24 +1552,6 @@
       <c r="J20" t="n">
         <v>58.92</v>
       </c>
-      <c r="K20" t="n">
-        <v/>
-      </c>
-      <c r="L20" t="n">
-        <v/>
-      </c>
-      <c r="M20" t="n">
-        <v/>
-      </c>
-      <c r="N20" t="n">
-        <v/>
-      </c>
-      <c r="O20" t="n">
-        <v/>
-      </c>
-      <c r="P20" t="n">
-        <v/>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>D0=58.92; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -1903,24 +1603,6 @@
       <c r="J21" t="n">
         <v>13.89</v>
       </c>
-      <c r="K21" t="n">
-        <v/>
-      </c>
-      <c r="L21" t="n">
-        <v/>
-      </c>
-      <c r="M21" t="n">
-        <v/>
-      </c>
-      <c r="N21" t="n">
-        <v/>
-      </c>
-      <c r="O21" t="n">
-        <v/>
-      </c>
-      <c r="P21" t="n">
-        <v/>
-      </c>
       <c r="Q21" t="inlineStr">
         <is>
           <t>D0=13.89; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -1972,24 +1654,6 @@
       <c r="J22" t="n">
         <v>15.58</v>
       </c>
-      <c r="K22" t="n">
-        <v/>
-      </c>
-      <c r="L22" t="n">
-        <v/>
-      </c>
-      <c r="M22" t="n">
-        <v/>
-      </c>
-      <c r="N22" t="n">
-        <v/>
-      </c>
-      <c r="O22" t="n">
-        <v/>
-      </c>
-      <c r="P22" t="n">
-        <v/>
-      </c>
       <c r="Q22" t="inlineStr">
         <is>
           <t>D0=15.58; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -2041,24 +1705,12 @@
       <c r="J23" s="5" t="n">
         <v>155.71</v>
       </c>
-      <c r="K23" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L23" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M23" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N23" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O23" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P23" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K23" s="5" t="n"/>
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="5" t="n"/>
+      <c r="O23" s="5" t="n"/>
+      <c r="P23" s="5" t="n"/>
       <c r="Q23" s="5" t="inlineStr">
         <is>
           <t>D0=155.71; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -2110,24 +1762,12 @@
       <c r="J24" s="5" t="n">
         <v>188.39</v>
       </c>
-      <c r="K24" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L24" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M24" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N24" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O24" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P24" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="5" t="n"/>
+      <c r="O24" s="5" t="n"/>
+      <c r="P24" s="5" t="n"/>
       <c r="Q24" s="5" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-06-01; 相对D0=-7.16%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -2179,24 +1819,6 @@
       <c r="J25" t="n">
         <v>163.09</v>
       </c>
-      <c r="K25" t="n">
-        <v/>
-      </c>
-      <c r="L25" t="n">
-        <v/>
-      </c>
-      <c r="M25" t="n">
-        <v/>
-      </c>
-      <c r="N25" t="n">
-        <v/>
-      </c>
-      <c r="O25" t="n">
-        <v/>
-      </c>
-      <c r="P25" t="n">
-        <v/>
-      </c>
       <c r="Q25" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-06-01; 相对D0=-2.56%; 历史重复2次; 重复日期=2026-05-26, 2026-05-29</t>
@@ -2248,24 +1870,6 @@
       <c r="J26" t="n">
         <v>54.5</v>
       </c>
-      <c r="K26" t="n">
-        <v/>
-      </c>
-      <c r="L26" t="n">
-        <v/>
-      </c>
-      <c r="M26" t="n">
-        <v/>
-      </c>
-      <c r="N26" t="n">
-        <v/>
-      </c>
-      <c r="O26" t="n">
-        <v/>
-      </c>
-      <c r="P26" t="n">
-        <v/>
-      </c>
       <c r="Q26" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-06-01; 相对D0=17.13%</t>
@@ -2317,24 +1921,6 @@
       <c r="J27" t="n">
         <v>16.62</v>
       </c>
-      <c r="K27" t="n">
-        <v/>
-      </c>
-      <c r="L27" t="n">
-        <v/>
-      </c>
-      <c r="M27" t="n">
-        <v/>
-      </c>
-      <c r="N27" t="n">
-        <v/>
-      </c>
-      <c r="O27" t="n">
-        <v/>
-      </c>
-      <c r="P27" t="n">
-        <v/>
-      </c>
       <c r="Q27" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-06-01; 相对D0=3.10%; 历史重复1次; 重复日期=2026-05-27</t>
@@ -2386,24 +1972,12 @@
       <c r="J28" s="5" t="n">
         <v>209.6</v>
       </c>
-      <c r="K28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P28" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K28" s="5" t="n"/>
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
+      <c r="N28" s="5" t="n"/>
+      <c r="O28" s="5" t="n"/>
+      <c r="P28" s="5" t="n"/>
       <c r="Q28" s="5" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-06-01; 相对D0=16.40%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -2455,24 +2029,6 @@
       <c r="J29" t="n">
         <v>47.585</v>
       </c>
-      <c r="K29" t="n">
-        <v/>
-      </c>
-      <c r="L29" t="n">
-        <v/>
-      </c>
-      <c r="M29" t="n">
-        <v/>
-      </c>
-      <c r="N29" t="n">
-        <v/>
-      </c>
-      <c r="O29" t="n">
-        <v/>
-      </c>
-      <c r="P29" t="n">
-        <v/>
-      </c>
       <c r="Q29" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-06-01; 相对D0=-1.11%; 历史重复2次; 重复日期=2026-05-26, 2026-05-29</t>
@@ -2524,24 +2080,6 @@
       <c r="J30" t="n">
         <v>400.08</v>
       </c>
-      <c r="K30" t="n">
-        <v/>
-      </c>
-      <c r="L30" t="n">
-        <v/>
-      </c>
-      <c r="M30" t="n">
-        <v/>
-      </c>
-      <c r="N30" t="n">
-        <v/>
-      </c>
-      <c r="O30" t="n">
-        <v/>
-      </c>
-      <c r="P30" t="n">
-        <v/>
-      </c>
       <c r="Q30" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-06-01; 相对D0=2.23%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -2593,24 +2131,6 @@
       <c r="J31" t="n">
         <v>950.54</v>
       </c>
-      <c r="K31" t="n">
-        <v/>
-      </c>
-      <c r="L31" t="n">
-        <v/>
-      </c>
-      <c r="M31" t="n">
-        <v/>
-      </c>
-      <c r="N31" t="n">
-        <v/>
-      </c>
-      <c r="O31" t="n">
-        <v/>
-      </c>
-      <c r="P31" t="n">
-        <v/>
-      </c>
       <c r="Q31" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-06-01; 相对D0=-8.49%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -2662,24 +2182,12 @@
       <c r="J32" s="5" t="n">
         <v>403.88</v>
       </c>
-      <c r="K32" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L32" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M32" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N32" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O32" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P32" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K32" s="5" t="n"/>
+      <c r="L32" s="5" t="n"/>
+      <c r="M32" s="5" t="n"/>
+      <c r="N32" s="5" t="n"/>
+      <c r="O32" s="5" t="n"/>
+      <c r="P32" s="5" t="n"/>
       <c r="Q32" s="5" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-06-01; 相对D0=23.84%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -2731,24 +2239,6 @@
       <c r="J33" t="n">
         <v>23.33</v>
       </c>
-      <c r="K33" t="n">
-        <v/>
-      </c>
-      <c r="L33" t="n">
-        <v/>
-      </c>
-      <c r="M33" t="n">
-        <v/>
-      </c>
-      <c r="N33" t="n">
-        <v/>
-      </c>
-      <c r="O33" t="n">
-        <v/>
-      </c>
-      <c r="P33" t="n">
-        <v/>
-      </c>
       <c r="Q33" t="inlineStr">
         <is>
           <t>D0=22.51; 最新=2026-06-01; 相对D0=3.64%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -2800,24 +2290,6 @@
       <c r="J34" t="n">
         <v>251.49</v>
       </c>
-      <c r="K34" t="n">
-        <v/>
-      </c>
-      <c r="L34" t="n">
-        <v/>
-      </c>
-      <c r="M34" t="n">
-        <v/>
-      </c>
-      <c r="N34" t="n">
-        <v/>
-      </c>
-      <c r="O34" t="n">
-        <v/>
-      </c>
-      <c r="P34" t="n">
-        <v/>
-      </c>
       <c r="Q34" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-06-01; 相对D0=8.40%</t>
@@ -2869,24 +2341,6 @@
       <c r="J35" t="n">
         <v>145.02</v>
       </c>
-      <c r="K35" t="n">
-        <v/>
-      </c>
-      <c r="L35" t="n">
-        <v/>
-      </c>
-      <c r="M35" t="n">
-        <v/>
-      </c>
-      <c r="N35" t="n">
-        <v/>
-      </c>
-      <c r="O35" t="n">
-        <v/>
-      </c>
-      <c r="P35" t="n">
-        <v/>
-      </c>
       <c r="Q35" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-06-01; 相对D0=11.13%</t>
@@ -2938,24 +2392,6 @@
       <c r="J36" t="n">
         <v>255.71</v>
       </c>
-      <c r="K36" t="n">
-        <v/>
-      </c>
-      <c r="L36" t="n">
-        <v/>
-      </c>
-      <c r="M36" t="n">
-        <v/>
-      </c>
-      <c r="N36" t="n">
-        <v/>
-      </c>
-      <c r="O36" t="n">
-        <v/>
-      </c>
-      <c r="P36" t="n">
-        <v/>
-      </c>
       <c r="Q36" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-06-01; 相对D0=-2.49%; 历史重复2次; 重复日期=2026-05-26, 2026-05-27</t>
@@ -3007,24 +2443,12 @@
       <c r="J37" s="5" t="n">
         <v>115.95</v>
       </c>
-      <c r="K37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P37" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K37" s="5" t="n"/>
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="n"/>
+      <c r="N37" s="5" t="n"/>
+      <c r="O37" s="5" t="n"/>
+      <c r="P37" s="5" t="n"/>
       <c r="Q37" s="5" t="inlineStr">
         <is>
           <t>D0=85.42; 最新=2026-06-01; 相对D0=35.74%; 历史重复1次; 重复日期=2026-05-27</t>
@@ -3076,24 +2500,12 @@
       <c r="J38" s="5" t="n">
         <v>415.88</v>
       </c>
-      <c r="K38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P38" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K38" s="5" t="n"/>
+      <c r="L38" s="5" t="n"/>
+      <c r="M38" s="5" t="n"/>
+      <c r="N38" s="5" t="n"/>
+      <c r="O38" s="5" t="n"/>
+      <c r="P38" s="5" t="n"/>
       <c r="Q38" s="5" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-06-01; 相对D0=-2.38%</t>
@@ -3145,24 +2557,12 @@
       <c r="J39" s="5" t="n">
         <v>13.59</v>
       </c>
-      <c r="K39" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L39" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M39" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N39" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O39" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P39" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K39" s="5" t="n"/>
+      <c r="L39" s="5" t="n"/>
+      <c r="M39" s="5" t="n"/>
+      <c r="N39" s="5" t="n"/>
+      <c r="O39" s="5" t="n"/>
+      <c r="P39" s="5" t="n"/>
       <c r="Q39" s="5" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-06-01; 相对D0=4.38%; 历史重复2次; 重复日期=2026-05-26, 2026-05-29</t>
@@ -3214,24 +2614,6 @@
       <c r="J40" t="n">
         <v>459.97</v>
       </c>
-      <c r="K40" t="n">
-        <v/>
-      </c>
-      <c r="L40" t="n">
-        <v/>
-      </c>
-      <c r="M40" t="n">
-        <v/>
-      </c>
-      <c r="N40" t="n">
-        <v/>
-      </c>
-      <c r="O40" t="n">
-        <v/>
-      </c>
-      <c r="P40" t="n">
-        <v/>
-      </c>
       <c r="Q40" t="inlineStr">
         <is>
           <t>D0=422.01; 最新=2026-06-01; 相对D0=9.00%</t>
@@ -3283,24 +2665,6 @@
       <c r="J41" t="n">
         <v>91.22</v>
       </c>
-      <c r="K41" t="n">
-        <v/>
-      </c>
-      <c r="L41" t="n">
-        <v/>
-      </c>
-      <c r="M41" t="n">
-        <v/>
-      </c>
-      <c r="N41" t="n">
-        <v/>
-      </c>
-      <c r="O41" t="n">
-        <v/>
-      </c>
-      <c r="P41" t="n">
-        <v/>
-      </c>
       <c r="Q41" t="inlineStr">
         <is>
           <t>D0=86.49; 最新=2026-06-01; 相对D0=5.47%</t>
@@ -3352,24 +2716,12 @@
       <c r="J42" s="5" t="n">
         <v>112.59</v>
       </c>
-      <c r="K42" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L42" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M42" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N42" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O42" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P42" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K42" s="5" t="n"/>
+      <c r="L42" s="5" t="n"/>
+      <c r="M42" s="5" t="n"/>
+      <c r="N42" s="5" t="n"/>
+      <c r="O42" s="5" t="n"/>
+      <c r="P42" s="5" t="n"/>
       <c r="Q42" s="5" t="inlineStr">
         <is>
           <t>D0=108.17; 最新=2026-06-01; 相对D0=4.09%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -3421,24 +2773,6 @@
       <c r="J43" t="n">
         <v>124.82</v>
       </c>
-      <c r="K43" t="n">
-        <v/>
-      </c>
-      <c r="L43" t="n">
-        <v/>
-      </c>
-      <c r="M43" t="n">
-        <v/>
-      </c>
-      <c r="N43" t="n">
-        <v/>
-      </c>
-      <c r="O43" t="n">
-        <v/>
-      </c>
-      <c r="P43" t="n">
-        <v/>
-      </c>
       <c r="Q43" t="inlineStr">
         <is>
           <t>D0=105.89; 最新=2026-06-01; 相对D0=17.88%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -3486,24 +2820,12 @@
       <c r="J44" s="5" t="n">
         <v>86.77</v>
       </c>
-      <c r="K44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P44" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K44" s="5" t="n"/>
+      <c r="L44" s="5" t="n"/>
+      <c r="M44" s="5" t="n"/>
+      <c r="N44" s="5" t="n"/>
+      <c r="O44" s="5" t="n"/>
+      <c r="P44" s="5" t="n"/>
       <c r="Q44" s="5" t="inlineStr">
         <is>
           <t>D0=88.50; 最新=2026-06-01; 相对D0=-1.95%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -3551,24 +2873,12 @@
       <c r="J45" s="5" t="n">
         <v>147.69</v>
       </c>
-      <c r="K45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P45" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K45" s="5" t="n"/>
+      <c r="L45" s="5" t="n"/>
+      <c r="M45" s="5" t="n"/>
+      <c r="N45" s="5" t="n"/>
+      <c r="O45" s="5" t="n"/>
+      <c r="P45" s="5" t="n"/>
       <c r="Q45" s="5" t="inlineStr">
         <is>
           <t>D0=158.34; 最新=2026-06-01; 相对D0=-6.73%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -3620,24 +2930,12 @@
       <c r="J46" s="5" t="n">
         <v>376.37</v>
       </c>
-      <c r="K46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P46" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K46" s="5" t="n"/>
+      <c r="L46" s="5" t="n"/>
+      <c r="M46" s="5" t="n"/>
+      <c r="N46" s="5" t="n"/>
+      <c r="O46" s="5" t="n"/>
+      <c r="P46" s="5" t="n"/>
       <c r="Q46" s="5" t="inlineStr">
         <is>
           <t>D0=388.88; 最新=2026-06-01; 相对D0=-3.22%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -3689,24 +2987,12 @@
       <c r="J47" s="5" t="n">
         <v>600.47</v>
       </c>
-      <c r="K47" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L47" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M47" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N47" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O47" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P47" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K47" s="5" t="n"/>
+      <c r="L47" s="5" t="n"/>
+      <c r="M47" s="5" t="n"/>
+      <c r="N47" s="5" t="n"/>
+      <c r="O47" s="5" t="n"/>
+      <c r="P47" s="5" t="n"/>
       <c r="Q47" s="5" t="inlineStr">
         <is>
           <t>D0=612.34; 最新=2026-06-01; 相对D0=-1.94%</t>
@@ -3758,24 +3044,6 @@
       <c r="J48" t="n">
         <v>108.96</v>
       </c>
-      <c r="K48" t="n">
-        <v/>
-      </c>
-      <c r="L48" t="n">
-        <v/>
-      </c>
-      <c r="M48" t="n">
-        <v/>
-      </c>
-      <c r="N48" t="n">
-        <v/>
-      </c>
-      <c r="O48" t="n">
-        <v/>
-      </c>
-      <c r="P48" t="n">
-        <v/>
-      </c>
       <c r="Q48" t="inlineStr">
         <is>
           <t>D0=106.94; 最新=2026-06-01; 相对D0=1.89%</t>
@@ -3827,24 +3095,12 @@
       <c r="J49" s="5" t="n">
         <v>12.89</v>
       </c>
-      <c r="K49" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L49" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M49" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N49" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O49" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P49" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K49" s="5" t="n"/>
+      <c r="L49" s="5" t="n"/>
+      <c r="M49" s="5" t="n"/>
+      <c r="N49" s="5" t="n"/>
+      <c r="O49" s="5" t="n"/>
+      <c r="P49" s="5" t="n"/>
       <c r="Q49" s="5" t="inlineStr">
         <is>
           <t>D0=12.22; 最新=2026-06-01; 相对D0=5.48%</t>
@@ -3896,24 +3152,6 @@
       <c r="J50" t="n">
         <v>83.78</v>
       </c>
-      <c r="K50" t="n">
-        <v/>
-      </c>
-      <c r="L50" t="n">
-        <v/>
-      </c>
-      <c r="M50" t="n">
-        <v/>
-      </c>
-      <c r="N50" t="n">
-        <v/>
-      </c>
-      <c r="O50" t="n">
-        <v/>
-      </c>
-      <c r="P50" t="n">
-        <v/>
-      </c>
       <c r="Q50" t="inlineStr">
         <is>
           <t>D0=84.64; 最新=2026-06-01; 相对D0=-1.02%</t>
@@ -3965,24 +3203,12 @@
       <c r="J51" s="5" t="n">
         <v>261.26</v>
       </c>
-      <c r="K51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P51" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K51" s="5" t="n"/>
+      <c r="L51" s="5" t="n"/>
+      <c r="M51" s="5" t="n"/>
+      <c r="N51" s="5" t="n"/>
+      <c r="O51" s="5" t="n"/>
+      <c r="P51" s="5" t="n"/>
       <c r="Q51" s="5" t="inlineStr">
         <is>
           <t>D0=271.85; 最新=2026-06-01; 相对D0=-3.90%</t>
@@ -4030,24 +3256,12 @@
       <c r="J52" s="5" t="n">
         <v>91.03</v>
       </c>
-      <c r="K52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P52" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K52" s="5" t="n"/>
+      <c r="L52" s="5" t="n"/>
+      <c r="M52" s="5" t="n"/>
+      <c r="N52" s="5" t="n"/>
+      <c r="O52" s="5" t="n"/>
+      <c r="P52" s="5" t="n"/>
       <c r="Q52" s="5" t="inlineStr">
         <is>
           <t>D0=90.87; 最新=2026-06-01; 相对D0=0.18%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -4095,24 +3309,12 @@
       <c r="J53" s="5" t="n">
         <v>38.79</v>
       </c>
-      <c r="K53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P53" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K53" s="5" t="n"/>
+      <c r="L53" s="5" t="n"/>
+      <c r="M53" s="5" t="n"/>
+      <c r="N53" s="5" t="n"/>
+      <c r="O53" s="5" t="n"/>
+      <c r="P53" s="5" t="n"/>
       <c r="Q53" s="5" t="inlineStr">
         <is>
           <t>D0=41.35; 最新=2026-06-01; 相对D0=-6.19%; 历史重复1次; 重复日期=2026-06-01</t>
@@ -4164,24 +3366,12 @@
       <c r="J54" s="5" t="n">
         <v>135.86</v>
       </c>
-      <c r="K54" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L54" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M54" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N54" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O54" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P54" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K54" s="5" t="n"/>
+      <c r="L54" s="5" t="n"/>
+      <c r="M54" s="5" t="n"/>
+      <c r="N54" s="5" t="n"/>
+      <c r="O54" s="5" t="n"/>
+      <c r="P54" s="5" t="n"/>
       <c r="Q54" s="5" t="inlineStr">
         <is>
           <t>D0=102.12; 最新=2026-06-01; 相对D0=33.04%</t>
@@ -4233,24 +3423,6 @@
       <c r="J55" t="n">
         <v>248.13</v>
       </c>
-      <c r="K55" t="n">
-        <v/>
-      </c>
-      <c r="L55" t="n">
-        <v/>
-      </c>
-      <c r="M55" t="n">
-        <v/>
-      </c>
-      <c r="N55" t="n">
-        <v/>
-      </c>
-      <c r="O55" t="n">
-        <v/>
-      </c>
-      <c r="P55" t="n">
-        <v/>
-      </c>
       <c r="Q55" t="inlineStr">
         <is>
           <t>D0=190.96; 最新=2026-06-01; 相对D0=29.94%</t>
@@ -4302,24 +3474,6 @@
       <c r="J56" t="n">
         <v>273.51</v>
       </c>
-      <c r="K56" t="n">
-        <v/>
-      </c>
-      <c r="L56" t="n">
-        <v/>
-      </c>
-      <c r="M56" t="n">
-        <v/>
-      </c>
-      <c r="N56" t="n">
-        <v/>
-      </c>
-      <c r="O56" t="n">
-        <v/>
-      </c>
-      <c r="P56" t="n">
-        <v/>
-      </c>
       <c r="Q56" t="inlineStr">
         <is>
           <t>D0=290.01; 最新=2026-06-01; 相对D0=-5.69%</t>
@@ -4371,24 +3525,12 @@
       <c r="J57" s="5" t="n">
         <v>782.17</v>
       </c>
-      <c r="K57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P57" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K57" s="5" t="n"/>
+      <c r="L57" s="5" t="n"/>
+      <c r="M57" s="5" t="n"/>
+      <c r="N57" s="5" t="n"/>
+      <c r="O57" s="5" t="n"/>
+      <c r="P57" s="5" t="n"/>
       <c r="Q57" s="5" t="inlineStr">
         <is>
           <t>D0=671.00; 最新=2026-06-01; 相对D0=16.57%</t>
@@ -4440,24 +3582,6 @@
       <c r="J58" t="n">
         <v>64.61</v>
       </c>
-      <c r="K58" t="n">
-        <v/>
-      </c>
-      <c r="L58" t="n">
-        <v/>
-      </c>
-      <c r="M58" t="n">
-        <v/>
-      </c>
-      <c r="N58" t="n">
-        <v/>
-      </c>
-      <c r="O58" t="n">
-        <v/>
-      </c>
-      <c r="P58" t="n">
-        <v/>
-      </c>
       <c r="Q58" t="inlineStr">
         <is>
           <t>D0=67.38; 最新=2026-06-01; 相对D0=-4.11%</t>
@@ -4505,24 +3629,12 @@
       <c r="J59" s="5" t="n">
         <v>1050.77</v>
       </c>
-      <c r="K59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P59" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K59" s="5" t="n"/>
+      <c r="L59" s="5" t="n"/>
+      <c r="M59" s="5" t="n"/>
+      <c r="N59" s="5" t="n"/>
+      <c r="O59" s="5" t="n"/>
+      <c r="P59" s="5" t="n"/>
       <c r="Q59" s="5" t="inlineStr">
         <is>
           <t>D0=1069.44; 最新=2026-06-01; 相对D0=-1.75%</t>
@@ -4574,24 +3686,12 @@
       <c r="J60" s="5" t="n">
         <v>147.14</v>
       </c>
-      <c r="K60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P60" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K60" s="5" t="n"/>
+      <c r="L60" s="5" t="n"/>
+      <c r="M60" s="5" t="n"/>
+      <c r="N60" s="5" t="n"/>
+      <c r="O60" s="5" t="n"/>
+      <c r="P60" s="5" t="n"/>
       <c r="Q60" s="5" t="inlineStr">
         <is>
           <t>D0=129.70; 最新=2026-06-01; 相对D0=13.45%</t>
@@ -4643,24 +3743,12 @@
       <c r="J61" s="5" t="n">
         <v>107.7</v>
       </c>
-      <c r="K61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P61" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K61" s="5" t="n"/>
+      <c r="L61" s="5" t="n"/>
+      <c r="M61" s="5" t="n"/>
+      <c r="N61" s="5" t="n"/>
+      <c r="O61" s="5" t="n"/>
+      <c r="P61" s="5" t="n"/>
       <c r="Q61" s="5" t="inlineStr">
         <is>
           <t>D0=95.68; 最新=2026-06-01; 相对D0=12.56%</t>
@@ -4712,24 +3800,12 @@
       <c r="J62" s="5" t="n">
         <v>460.52</v>
       </c>
-      <c r="K62" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L62" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M62" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N62" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O62" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P62" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K62" s="5" t="n"/>
+      <c r="L62" s="5" t="n"/>
+      <c r="M62" s="5" t="n"/>
+      <c r="N62" s="5" t="n"/>
+      <c r="O62" s="5" t="n"/>
+      <c r="P62" s="5" t="n"/>
       <c r="Q62" s="5" t="inlineStr">
         <is>
           <t>D0=426.99; 最新=2026-06-01; 相对D0=7.85%</t>
@@ -4781,24 +3857,6 @@
       <c r="J63" t="n">
         <v>264.51</v>
       </c>
-      <c r="K63" t="n">
-        <v/>
-      </c>
-      <c r="L63" t="n">
-        <v/>
-      </c>
-      <c r="M63" t="n">
-        <v/>
-      </c>
-      <c r="N63" t="n">
-        <v/>
-      </c>
-      <c r="O63" t="n">
-        <v/>
-      </c>
-      <c r="P63" t="n">
-        <v/>
-      </c>
       <c r="Q63" t="inlineStr">
         <is>
           <t>D0=226.34; 最新=2026-06-01; 相对D0=16.86%</t>
@@ -4850,24 +3908,12 @@
       <c r="J64" s="5" t="n">
         <v>139.79</v>
       </c>
-      <c r="K64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P64" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K64" s="5" t="n"/>
+      <c r="L64" s="5" t="n"/>
+      <c r="M64" s="5" t="n"/>
+      <c r="N64" s="5" t="n"/>
+      <c r="O64" s="5" t="n"/>
+      <c r="P64" s="5" t="n"/>
       <c r="Q64" s="5" t="inlineStr">
         <is>
           <t>D0=94.72; 最新=2026-06-01; 相对D0=47.58%</t>
@@ -4919,24 +3965,12 @@
       <c r="J65" s="5" t="n">
         <v>300.48</v>
       </c>
-      <c r="K65" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L65" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M65" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N65" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O65" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P65" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K65" s="5" t="n"/>
+      <c r="L65" s="5" t="n"/>
+      <c r="M65" s="5" t="n"/>
+      <c r="N65" s="5" t="n"/>
+      <c r="O65" s="5" t="n"/>
+      <c r="P65" s="5" t="n"/>
       <c r="Q65" s="5" t="inlineStr">
         <is>
           <t>D0=257.77; 最新=2026-06-01; 相对D0=16.57%</t>
@@ -4988,24 +4022,12 @@
       <c r="J66" s="5" t="n">
         <v>160.65</v>
       </c>
-      <c r="K66" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L66" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M66" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N66" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O66" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P66" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K66" s="5" t="n"/>
+      <c r="L66" s="5" t="n"/>
+      <c r="M66" s="5" t="n"/>
+      <c r="N66" s="5" t="n"/>
+      <c r="O66" s="5" t="n"/>
+      <c r="P66" s="5" t="n"/>
       <c r="Q66" s="5" t="inlineStr">
         <is>
           <t>D0=143.34; 最新=2026-06-01; 相对D0=12.08%</t>
@@ -5057,24 +4079,12 @@
       <c r="J67" s="5" t="n">
         <v>274.03</v>
       </c>
-      <c r="K67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P67" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K67" s="5" t="n"/>
+      <c r="L67" s="5" t="n"/>
+      <c r="M67" s="5" t="n"/>
+      <c r="N67" s="5" t="n"/>
+      <c r="O67" s="5" t="n"/>
+      <c r="P67" s="5" t="n"/>
       <c r="Q67" s="5" t="inlineStr">
         <is>
           <t>D0=259.21; 最新=2026-06-01; 相对D0=5.72%</t>
@@ -5126,24 +4136,12 @@
       <c r="J68" s="5" t="n">
         <v>265.7</v>
       </c>
-      <c r="K68" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L68" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M68" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N68" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O68" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P68" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K68" s="5" t="n"/>
+      <c r="L68" s="5" t="n"/>
+      <c r="M68" s="5" t="n"/>
+      <c r="N68" s="5" t="n"/>
+      <c r="O68" s="5" t="n"/>
+      <c r="P68" s="5" t="n"/>
       <c r="Q68" s="5" t="inlineStr">
         <is>
           <t>D0=287.75; 最新=2026-06-01; 相对D0=-7.66%</t>
@@ -5195,24 +4193,6 @@
       <c r="J69" t="n">
         <v>115.58</v>
       </c>
-      <c r="K69" t="n">
-        <v/>
-      </c>
-      <c r="L69" t="n">
-        <v/>
-      </c>
-      <c r="M69" t="n">
-        <v/>
-      </c>
-      <c r="N69" t="n">
-        <v/>
-      </c>
-      <c r="O69" t="n">
-        <v/>
-      </c>
-      <c r="P69" t="n">
-        <v/>
-      </c>
       <c r="Q69" t="inlineStr">
         <is>
           <t>D0=115.58; 最新=2026-06-01; 相对D0=0.00%</t>
@@ -5260,24 +4240,12 @@
       <c r="J70" s="5" t="n">
         <v>99.17700000000001</v>
       </c>
-      <c r="K70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P70" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K70" s="5" t="n"/>
+      <c r="L70" s="5" t="n"/>
+      <c r="M70" s="5" t="n"/>
+      <c r="N70" s="5" t="n"/>
+      <c r="O70" s="5" t="n"/>
+      <c r="P70" s="5" t="n"/>
       <c r="Q70" s="5" t="inlineStr">
         <is>
           <t>D0=99.18; 最新=2026-06-01; 相对D0=0.00%</t>
@@ -5325,24 +4293,12 @@
       <c r="J71" s="5" t="n">
         <v>16.01</v>
       </c>
-      <c r="K71" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L71" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M71" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N71" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O71" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P71" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K71" s="5" t="n"/>
+      <c r="L71" s="5" t="n"/>
+      <c r="M71" s="5" t="n"/>
+      <c r="N71" s="5" t="n"/>
+      <c r="O71" s="5" t="n"/>
+      <c r="P71" s="5" t="n"/>
       <c r="Q71" s="5" t="inlineStr">
         <is>
           <t>D0=16.01; 最新=2026-06-01; 相对D0=0.00%</t>
@@ -5579,24 +4535,12 @@
       <c r="J83" s="5" t="n">
         <v>163.09</v>
       </c>
-      <c r="K83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P83" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K83" s="5" t="n"/>
+      <c r="L83" s="5" t="n"/>
+      <c r="M83" s="5" t="n"/>
+      <c r="N83" s="5" t="n"/>
+      <c r="O83" s="5" t="n"/>
+      <c r="P83" s="5" t="n"/>
       <c r="Q83" s="5" t="inlineStr">
         <is>
           <t>D0=171.66; 最新=2026-06-01; 相对D0=-4.99%; 本次触发=2026-06-01(正式卖出); 历史重复1次; 重复日期=2026-06-01</t>
@@ -5648,24 +4592,6 @@
       <c r="J84" t="n">
         <v>105.65</v>
       </c>
-      <c r="K84" t="n">
-        <v/>
-      </c>
-      <c r="L84" t="n">
-        <v/>
-      </c>
-      <c r="M84" t="n">
-        <v/>
-      </c>
-      <c r="N84" t="n">
-        <v/>
-      </c>
-      <c r="O84" t="n">
-        <v/>
-      </c>
-      <c r="P84" t="n">
-        <v/>
-      </c>
       <c r="Q84" t="inlineStr">
         <is>
           <t>D0=105.65; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出)</t>
@@ -5717,24 +4643,6 @@
       <c r="J85" t="n">
         <v>64.61</v>
       </c>
-      <c r="K85" t="n">
-        <v/>
-      </c>
-      <c r="L85" t="n">
-        <v/>
-      </c>
-      <c r="M85" t="n">
-        <v/>
-      </c>
-      <c r="N85" t="n">
-        <v/>
-      </c>
-      <c r="O85" t="n">
-        <v/>
-      </c>
-      <c r="P85" t="n">
-        <v/>
-      </c>
       <c r="Q85" t="inlineStr">
         <is>
           <t>D0=64.61; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出)</t>
@@ -5786,24 +4694,12 @@
       <c r="J86" s="5" t="n">
         <v>135.73</v>
       </c>
-      <c r="K86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P86" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K86" s="5" t="n"/>
+      <c r="L86" s="5" t="n"/>
+      <c r="M86" s="5" t="n"/>
+      <c r="N86" s="5" t="n"/>
+      <c r="O86" s="5" t="n"/>
+      <c r="P86" s="5" t="n"/>
       <c r="Q86" s="5" t="inlineStr">
         <is>
           <t>D0=135.73; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出 | 预警卖出)</t>
@@ -5855,24 +4751,12 @@
       <c r="J87" s="5" t="n">
         <v>600.47</v>
       </c>
-      <c r="K87" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L87" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M87" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N87" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O87" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P87" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K87" s="5" t="n"/>
+      <c r="L87" s="5" t="n"/>
+      <c r="M87" s="5" t="n"/>
+      <c r="N87" s="5" t="n"/>
+      <c r="O87" s="5" t="n"/>
+      <c r="P87" s="5" t="n"/>
       <c r="Q87" s="5" t="inlineStr">
         <is>
           <t>D0=600.47; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出 | 预警卖出)</t>
@@ -5924,24 +4808,12 @@
       <c r="J88" s="5" t="n">
         <v>24.86</v>
       </c>
-      <c r="K88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P88" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K88" s="5" t="n"/>
+      <c r="L88" s="5" t="n"/>
+      <c r="M88" s="5" t="n"/>
+      <c r="N88" s="5" t="n"/>
+      <c r="O88" s="5" t="n"/>
+      <c r="P88" s="5" t="n"/>
       <c r="Q88" s="5" t="inlineStr">
         <is>
           <t>D0=24.86; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出)</t>
@@ -5993,24 +4865,12 @@
       <c r="J89" s="5" t="n">
         <v>415.88</v>
       </c>
-      <c r="K89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P89" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K89" s="5" t="n"/>
+      <c r="L89" s="5" t="n"/>
+      <c r="M89" s="5" t="n"/>
+      <c r="N89" s="5" t="n"/>
+      <c r="O89" s="5" t="n"/>
+      <c r="P89" s="5" t="n"/>
       <c r="Q89" s="5" t="inlineStr">
         <is>
           <t>D0=415.88; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出 | 预警卖出)</t>
@@ -6062,24 +4922,12 @@
       <c r="J90" s="5" t="n">
         <v>39.35</v>
       </c>
-      <c r="K90" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L90" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M90" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N90" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O90" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P90" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K90" s="5" t="n"/>
+      <c r="L90" s="5" t="n"/>
+      <c r="M90" s="5" t="n"/>
+      <c r="N90" s="5" t="n"/>
+      <c r="O90" s="5" t="n"/>
+      <c r="P90" s="5" t="n"/>
       <c r="Q90" s="5" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-06-01; 相对D0=-5.11%</t>
@@ -6100,7 +4948,6 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -6127,24 +4974,6 @@
       <c r="J91" t="n">
         <v>91.03</v>
       </c>
-      <c r="K91" t="n">
-        <v/>
-      </c>
-      <c r="L91" t="n">
-        <v/>
-      </c>
-      <c r="M91" t="n">
-        <v/>
-      </c>
-      <c r="N91" t="n">
-        <v/>
-      </c>
-      <c r="O91" t="n">
-        <v/>
-      </c>
-      <c r="P91" t="n">
-        <v/>
-      </c>
       <c r="Q91" t="inlineStr">
         <is>
           <t>D0=90.64; 最新=2026-06-01; 相对D0=0.43%</t>
@@ -6196,24 +5025,12 @@
       <c r="J92" s="5" t="n">
         <v>185.83</v>
       </c>
-      <c r="K92" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L92" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M92" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N92" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O92" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P92" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K92" s="5" t="n"/>
+      <c r="L92" s="5" t="n"/>
+      <c r="M92" s="5" t="n"/>
+      <c r="N92" s="5" t="n"/>
+      <c r="O92" s="5" t="n"/>
+      <c r="P92" s="5" t="n"/>
       <c r="Q92" s="5" t="inlineStr">
         <is>
           <t>D0=184.71; 最新=2026-06-01; 相对D0=0.61%</t>
@@ -6265,24 +5082,12 @@
       <c r="J93" s="5" t="n">
         <v>136.62</v>
       </c>
-      <c r="K93" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L93" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M93" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N93" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O93" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P93" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K93" s="5" t="n"/>
+      <c r="L93" s="5" t="n"/>
+      <c r="M93" s="5" t="n"/>
+      <c r="N93" s="5" t="n"/>
+      <c r="O93" s="5" t="n"/>
+      <c r="P93" s="5" t="n"/>
       <c r="Q93" s="5" t="inlineStr">
         <is>
           <t>D0=136.20; 最新=2026-06-01; 相对D0=0.31%</t>
@@ -6303,7 +5108,6 @@
           <t>GDXD</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -6330,24 +5134,6 @@
       <c r="J94" t="n">
         <v>38.79</v>
       </c>
-      <c r="K94" t="n">
-        <v/>
-      </c>
-      <c r="L94" t="n">
-        <v/>
-      </c>
-      <c r="M94" t="n">
-        <v/>
-      </c>
-      <c r="N94" t="n">
-        <v/>
-      </c>
-      <c r="O94" t="n">
-        <v/>
-      </c>
-      <c r="P94" t="n">
-        <v/>
-      </c>
       <c r="Q94" t="inlineStr">
         <is>
           <t>D0=37.61; 最新=2026-06-01; 相对D0=3.14%</t>
@@ -6399,24 +5185,6 @@
       <c r="J95" t="n">
         <v>403.88</v>
       </c>
-      <c r="K95" t="n">
-        <v/>
-      </c>
-      <c r="L95" t="n">
-        <v/>
-      </c>
-      <c r="M95" t="n">
-        <v/>
-      </c>
-      <c r="N95" t="n">
-        <v/>
-      </c>
-      <c r="O95" t="n">
-        <v/>
-      </c>
-      <c r="P95" t="n">
-        <v/>
-      </c>
       <c r="Q95" t="inlineStr">
         <is>
           <t>D0=307.35; 最新=2026-06-01; 相对D0=31.41%</t>
@@ -6468,24 +5236,12 @@
       <c r="J96" s="5" t="n">
         <v>58.92</v>
       </c>
-      <c r="K96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P96" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K96" s="5" t="n"/>
+      <c r="L96" s="5" t="n"/>
+      <c r="M96" s="5" t="n"/>
+      <c r="N96" s="5" t="n"/>
+      <c r="O96" s="5" t="n"/>
+      <c r="P96" s="5" t="n"/>
       <c r="Q96" s="5" t="inlineStr">
         <is>
           <t>D0=57.46; 最新=2026-06-01; 相对D0=2.54%</t>
@@ -6537,24 +5293,12 @@
       <c r="J97" s="5" t="n">
         <v>13.89</v>
       </c>
-      <c r="K97" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L97" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M97" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N97" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O97" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P97" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K97" s="5" t="n"/>
+      <c r="L97" s="5" t="n"/>
+      <c r="M97" s="5" t="n"/>
+      <c r="N97" s="5" t="n"/>
+      <c r="O97" s="5" t="n"/>
+      <c r="P97" s="5" t="n"/>
       <c r="Q97" s="5" t="inlineStr">
         <is>
           <t>D0=13.35; 最新=2026-06-01; 相对D0=4.04%</t>
@@ -6606,24 +5350,12 @@
       <c r="J98" s="5" t="n">
         <v>54.75</v>
       </c>
-      <c r="K98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P98" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K98" s="5" t="n"/>
+      <c r="L98" s="5" t="n"/>
+      <c r="M98" s="5" t="n"/>
+      <c r="N98" s="5" t="n"/>
+      <c r="O98" s="5" t="n"/>
+      <c r="P98" s="5" t="n"/>
       <c r="Q98" s="5" t="inlineStr">
         <is>
           <t>D0=56.50; 最新=2026-06-01; 相对D0=-3.10%</t>
@@ -6675,24 +5407,6 @@
       <c r="J99" t="n">
         <v>155.71</v>
       </c>
-      <c r="K99" t="n">
-        <v/>
-      </c>
-      <c r="L99" t="n">
-        <v/>
-      </c>
-      <c r="M99" t="n">
-        <v/>
-      </c>
-      <c r="N99" t="n">
-        <v/>
-      </c>
-      <c r="O99" t="n">
-        <v/>
-      </c>
-      <c r="P99" t="n">
-        <v/>
-      </c>
       <c r="Q99" t="inlineStr">
         <is>
           <t>D0=126.41; 最新=2026-06-01; 相对D0=23.18%</t>
@@ -6744,24 +5458,12 @@
       <c r="J100" s="5" t="n">
         <v>109.55</v>
       </c>
-      <c r="K100" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L100" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M100" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N100" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O100" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P100" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K100" s="5" t="n"/>
+      <c r="L100" s="5" t="n"/>
+      <c r="M100" s="5" t="n"/>
+      <c r="N100" s="5" t="n"/>
+      <c r="O100" s="5" t="n"/>
+      <c r="P100" s="5" t="n"/>
       <c r="Q100" s="5" t="inlineStr">
         <is>
           <t>D0=115.70; 最新=2026-06-01; 相对D0=-5.32%</t>
@@ -6813,24 +5515,6 @@
       <c r="J101" t="n">
         <v>265.7</v>
       </c>
-      <c r="K101" t="n">
-        <v/>
-      </c>
-      <c r="L101" t="n">
-        <v/>
-      </c>
-      <c r="M101" t="n">
-        <v/>
-      </c>
-      <c r="N101" t="n">
-        <v/>
-      </c>
-      <c r="O101" t="n">
-        <v/>
-      </c>
-      <c r="P101" t="n">
-        <v/>
-      </c>
       <c r="Q101" t="inlineStr">
         <is>
           <t>D0=286.31; 最新=2026-06-01; 相对D0=-7.20%</t>
@@ -6882,24 +5566,12 @@
       <c r="J102" s="5" t="n">
         <v>176.7</v>
       </c>
-      <c r="K102" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L102" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M102" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N102" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O102" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P102" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K102" s="5" t="n"/>
+      <c r="L102" s="5" t="n"/>
+      <c r="M102" s="5" t="n"/>
+      <c r="N102" s="5" t="n"/>
+      <c r="O102" s="5" t="n"/>
+      <c r="P102" s="5" t="n"/>
       <c r="Q102" s="5" t="inlineStr">
         <is>
           <t>D0=182.97; 最新=2026-06-01; 相对D0=-3.43%</t>
@@ -6951,24 +5623,6 @@
       <c r="J103" t="n">
         <v>492.29</v>
       </c>
-      <c r="K103" t="n">
-        <v/>
-      </c>
-      <c r="L103" t="n">
-        <v/>
-      </c>
-      <c r="M103" t="n">
-        <v/>
-      </c>
-      <c r="N103" t="n">
-        <v/>
-      </c>
-      <c r="O103" t="n">
-        <v/>
-      </c>
-      <c r="P103" t="n">
-        <v/>
-      </c>
       <c r="Q103" t="inlineStr">
         <is>
           <t>D0=480.64; 最新=2026-06-01; 相对D0=2.42%</t>
@@ -7020,24 +5674,12 @@
       <c r="J104" s="5" t="n">
         <v>93.62</v>
       </c>
-      <c r="K104" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L104" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M104" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N104" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O104" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P104" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K104" s="5" t="n"/>
+      <c r="L104" s="5" t="n"/>
+      <c r="M104" s="5" t="n"/>
+      <c r="N104" s="5" t="n"/>
+      <c r="O104" s="5" t="n"/>
+      <c r="P104" s="5" t="n"/>
       <c r="Q104" s="5" t="inlineStr">
         <is>
           <t>D0=92.33; 最新=2026-06-01; 相对D0=1.40%</t>
@@ -7089,24 +5731,12 @@
       <c r="J105" s="5" t="n">
         <v>72.75</v>
       </c>
-      <c r="K105" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L105" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M105" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N105" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O105" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P105" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K105" s="5" t="n"/>
+      <c r="L105" s="5" t="n"/>
+      <c r="M105" s="5" t="n"/>
+      <c r="N105" s="5" t="n"/>
+      <c r="O105" s="5" t="n"/>
+      <c r="P105" s="5" t="n"/>
       <c r="Q105" s="5" t="inlineStr">
         <is>
           <t>D0=69.56; 最新=2026-06-01; 相对D0=4.59%</t>
@@ -7158,24 +5788,6 @@
       <c r="J106" t="n">
         <v>273.51</v>
       </c>
-      <c r="K106" t="n">
-        <v/>
-      </c>
-      <c r="L106" t="n">
-        <v/>
-      </c>
-      <c r="M106" t="n">
-        <v/>
-      </c>
-      <c r="N106" t="n">
-        <v/>
-      </c>
-      <c r="O106" t="n">
-        <v/>
-      </c>
-      <c r="P106" t="n">
-        <v/>
-      </c>
       <c r="Q106" t="inlineStr">
         <is>
           <t>D0=285.00; 最新=2026-06-01; 相对D0=-4.03%</t>
@@ -7227,24 +5839,12 @@
       <c r="J107" s="5" t="n">
         <v>362.9</v>
       </c>
-      <c r="K107" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L107" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M107" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N107" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O107" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P107" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K107" s="5" t="n"/>
+      <c r="L107" s="5" t="n"/>
+      <c r="M107" s="5" t="n"/>
+      <c r="N107" s="5" t="n"/>
+      <c r="O107" s="5" t="n"/>
+      <c r="P107" s="5" t="n"/>
       <c r="Q107" s="5" t="inlineStr">
         <is>
           <t>D0=361.47; 最新=2026-06-01; 相对D0=0.40%</t>
@@ -7296,24 +5896,6 @@
       <c r="J108" t="n">
         <v>27.15</v>
       </c>
-      <c r="K108" t="n">
-        <v/>
-      </c>
-      <c r="L108" t="n">
-        <v/>
-      </c>
-      <c r="M108" t="n">
-        <v/>
-      </c>
-      <c r="N108" t="n">
-        <v/>
-      </c>
-      <c r="O108" t="n">
-        <v/>
-      </c>
-      <c r="P108" t="n">
-        <v/>
-      </c>
       <c r="Q108" t="inlineStr">
         <is>
           <t>D0=18.88; 最新=2026-06-01; 相对D0=43.80%</t>
@@ -7365,24 +5947,6 @@
       <c r="J109" t="n">
         <v>109.33</v>
       </c>
-      <c r="K109" t="n">
-        <v/>
-      </c>
-      <c r="L109" t="n">
-        <v/>
-      </c>
-      <c r="M109" t="n">
-        <v/>
-      </c>
-      <c r="N109" t="n">
-        <v/>
-      </c>
-      <c r="O109" t="n">
-        <v/>
-      </c>
-      <c r="P109" t="n">
-        <v/>
-      </c>
       <c r="Q109" t="inlineStr">
         <is>
           <t>D0=114.68; 最新=2026-06-01; 相对D0=-4.67%</t>
@@ -7434,24 +5998,12 @@
       <c r="J110" s="5" t="n">
         <v>129.47</v>
       </c>
-      <c r="K110" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L110" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M110" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N110" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O110" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P110" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K110" s="5" t="n"/>
+      <c r="L110" s="5" t="n"/>
+      <c r="M110" s="5" t="n"/>
+      <c r="N110" s="5" t="n"/>
+      <c r="O110" s="5" t="n"/>
+      <c r="P110" s="5" t="n"/>
       <c r="Q110" s="5" t="inlineStr">
         <is>
           <t>D0=134.08; 最新=2026-06-01; 相对D0=-3.44%</t>
@@ -7503,24 +6055,12 @@
       <c r="J111" s="5" t="n">
         <v>252.53</v>
       </c>
-      <c r="K111" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L111" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M111" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N111" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O111" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P111" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K111" s="5" t="n"/>
+      <c r="L111" s="5" t="n"/>
+      <c r="M111" s="5" t="n"/>
+      <c r="N111" s="5" t="n"/>
+      <c r="O111" s="5" t="n"/>
+      <c r="P111" s="5" t="n"/>
       <c r="Q111" s="5" t="inlineStr">
         <is>
           <t>D0=255.23; 最新=2026-06-01; 相对D0=-1.06%</t>
@@ -7617,7 +6157,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7629,7 +6168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -7727,9 +6266,7 @@
           <t>AMZN</t>
         </is>
       </c>
-      <c r="B3" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B3" s="17" t="n"/>
       <c r="C3" s="16" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -7774,9 +6311,7 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B4" s="10" t="n"/>
       <c r="C4" s="5" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -7825,9 +6360,7 @@
           <t>GDXD</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B5" s="17" t="n"/>
       <c r="C5" s="16" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -7876,9 +6409,7 @@
           <t>NOW</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B6" s="10" t="n"/>
       <c r="C6" s="5" t="inlineStr">
         <is>
           <t>11 AI软件 / SAAS</t>
@@ -7923,9 +6454,7 @@
           <t>ORCL</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B7" s="10" t="n"/>
       <c r="C7" s="5" t="inlineStr">
         <is>
           <t>21 数据中心</t>
@@ -8122,9 +6651,7 @@
           <t>SLB</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B18" s="10" t="n"/>
       <c r="C18" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -8169,9 +6696,7 @@
           <t>ZS</t>
         </is>
       </c>
-      <c r="B19" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B19" s="10" t="n"/>
       <c r="C19" s="5" t="inlineStr">
         <is>
           <t>12 网络安全</t>
@@ -8261,10 +6786,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8276,7 +6797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -8362,9 +6883,7 @@
           <t>BE</t>
         </is>
       </c>
-      <c r="B3" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B3" s="10" t="n"/>
       <c r="C3" s="5" t="inlineStr">
         <is>
           <t>09 储能</t>
@@ -8403,9 +6922,7 @@
           <t>CRWD</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B4" s="10" t="n"/>
       <c r="C4" s="5" t="inlineStr">
         <is>
           <t>12 网络安全</t>
@@ -8444,9 +6961,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B5" s="10" t="n"/>
       <c r="C5" s="5" t="inlineStr">
         <is>
           <t>15 公用事业</t>
@@ -8485,9 +7000,7 @@
           <t>EQIX</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B6" s="10" t="n"/>
       <c r="C6" s="5" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -8526,9 +7039,7 @@
           <t>FTNT</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B7" s="10" t="n"/>
       <c r="C7" s="5" t="inlineStr">
         <is>
           <t>12 网络安全</t>
@@ -8567,9 +7078,7 @@
           <t>IGV</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B8" s="10" t="n"/>
       <c r="C8" s="5" t="inlineStr">
         <is>
           <t>11 AI软件 / SAAS</t>
@@ -8608,9 +7117,7 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B9" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B9" s="17" t="n"/>
       <c r="C9" s="16" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -8649,9 +7156,7 @@
           <t>NBIS</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n">
-        <v/>
-      </c>
+      <c r="B10" s="13" t="n"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>21 数据中心</t>
@@ -8682,7 +7187,6 @@
       <c r="J10" s="15" t="n">
         <v>0.16864</v>
       </c>
-      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -8690,9 +7194,7 @@
           <t>OKTA</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B11" s="10" t="n"/>
       <c r="C11" s="5" t="inlineStr">
         <is>
           <t>12 网络安全</t>
@@ -8731,9 +7233,7 @@
           <t>PANW</t>
         </is>
       </c>
-      <c r="B12" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B12" s="10" t="n"/>
       <c r="C12" s="5" t="inlineStr">
         <is>
           <t>12 网络安全</t>
@@ -8772,9 +7272,7 @@
           <t>PLTR</t>
         </is>
       </c>
-      <c r="B13" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B13" s="17" t="n"/>
       <c r="C13" s="16" t="inlineStr">
         <is>
           <t>11 AI软件 / SAAS</t>
@@ -8968,9 +7466,7 @@
           <t>AXTI</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B25" s="10" t="n"/>
       <c r="C25" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -9009,9 +7505,7 @@
           <t>CEG</t>
         </is>
       </c>
-      <c r="B26" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B26" s="10" t="n"/>
       <c r="C26" s="5" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -9050,9 +7544,7 @@
           <t>GLW</t>
         </is>
       </c>
-      <c r="B27" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B27" s="10" t="n"/>
       <c r="C27" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -9091,9 +7583,7 @@
           <t>SNPS</t>
         </is>
       </c>
-      <c r="B28" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B28" s="10" t="n"/>
       <c r="C28" s="5" t="inlineStr">
         <is>
           <t>04 半导体设备 / EDA</t>
@@ -9190,9 +7680,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9204,7 +7691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -9278,9 +7765,7 @@
           <t>ADBE</t>
         </is>
       </c>
-      <c r="B3" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B3" s="17" t="n"/>
       <c r="C3" s="16" t="inlineStr">
         <is>
           <t>11 AI软件 / SAAS</t>
@@ -9293,7 +7778,7 @@
       </c>
       <c r="E3" s="18" t="inlineStr">
         <is>
-          <t>买入跟踪 | 正式买入 | 第一买入点 | 预警买入</t>
+          <t>买入跟踪 | 正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F3" s="16" t="n">
@@ -9313,9 +7798,7 @@
           <t>CEG</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B4" s="10" t="n"/>
       <c r="C4" s="5" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -9348,9 +7831,7 @@
           <t>NVDA</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B5" s="17" t="n"/>
       <c r="C5" s="16" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -9506,9 +7987,7 @@
           <t>AEHR</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B15" s="10" t="n"/>
       <c r="C15" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -9541,9 +8020,7 @@
           <t>AMKR</t>
         </is>
       </c>
-      <c r="B16" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B16" s="10" t="n"/>
       <c r="C16" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -9576,9 +8053,7 @@
           <t>BE</t>
         </is>
       </c>
-      <c r="B17" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B17" s="10" t="n"/>
       <c r="C17" s="5" t="inlineStr">
         <is>
           <t>09 储能</t>
@@ -9611,9 +8086,7 @@
           <t>CAMT</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B18" s="10" t="n"/>
       <c r="C18" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -9650,9 +8123,7 @@
           <t>COHR</t>
         </is>
       </c>
-      <c r="B19" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B19" s="10" t="n"/>
       <c r="C19" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -9685,9 +8156,7 @@
           <t>FLNC</t>
         </is>
       </c>
-      <c r="B20" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B20" s="10" t="n"/>
       <c r="C20" s="5" t="inlineStr">
         <is>
           <t>09 储能</t>
@@ -9720,9 +8189,7 @@
           <t>INTC</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B21" s="10" t="n"/>
       <c r="C21" s="5" t="inlineStr">
         <is>
           <t>03 GPU / AI芯片</t>
@@ -9755,9 +8222,7 @@
           <t>NRG</t>
         </is>
       </c>
-      <c r="B22" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B22" s="10" t="n"/>
       <c r="C22" s="5" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -9790,9 +8255,7 @@
           <t>TSEM</t>
         </is>
       </c>
-      <c r="B23" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B23" s="10" t="n"/>
       <c r="C23" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -9909,7 +8372,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9921,7 +8383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -9983,9 +8445,7 @@
           <t>AES</t>
         </is>
       </c>
-      <c r="B3" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B3" s="10" t="n"/>
       <c r="C3" s="5" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -10012,9 +8472,7 @@
           <t>AON</t>
         </is>
       </c>
-      <c r="B4" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B4" s="17" t="n"/>
       <c r="C4" s="16" t="inlineStr">
         <is>
           <t>16 金融股</t>
@@ -10041,9 +8499,7 @@
           <t>COP</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B5" s="10" t="n"/>
       <c r="C5" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -10070,9 +8526,7 @@
           <t>CVX</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B6" s="17" t="n"/>
       <c r="C6" s="16" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -10099,9 +8553,7 @@
           <t>DXY</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B7" s="17" t="n"/>
       <c r="C7" s="16" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -10128,9 +8580,7 @@
           <t>EOSE</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B8" s="10" t="n"/>
       <c r="C8" s="5" t="inlineStr">
         <is>
           <t>09 储能</t>
@@ -10157,9 +8607,7 @@
           <t>FLNC</t>
         </is>
       </c>
-      <c r="B9" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B9" s="17" t="n"/>
       <c r="C9" s="16" t="inlineStr">
         <is>
           <t>09 储能</t>
@@ -10186,9 +8634,7 @@
           <t>IHF</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B10" s="17" t="n"/>
       <c r="C10" s="16" t="inlineStr">
         <is>
           <t>20 医疗</t>
@@ -10215,9 +8661,7 @@
           <t>LITE</t>
         </is>
       </c>
-      <c r="B11" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B11" s="17" t="n"/>
       <c r="C11" s="16" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -10244,9 +8688,7 @@
           <t>LWLG</t>
         </is>
       </c>
-      <c r="B12" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B12" s="10" t="n"/>
       <c r="C12" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -10273,9 +8715,7 @@
           <t>NTR</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n">
-        <v/>
-      </c>
+      <c r="B13" s="13" t="n"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>18 化肥</t>
@@ -10294,7 +8734,6 @@
       <c r="F13" t="n">
         <v>69.56999999999999</v>
       </c>
-      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
@@ -10302,9 +8741,7 @@
           <t>OXY</t>
         </is>
       </c>
-      <c r="B14" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B14" s="17" t="n"/>
       <c r="C14" s="16" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -10331,9 +8768,7 @@
           <t>POET</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B15" s="17" t="n"/>
       <c r="C15" s="16" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -10360,9 +8795,7 @@
           <t>RUN</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n">
-        <v/>
-      </c>
+      <c r="B16" s="13" t="n"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>10 太阳能</t>
@@ -10381,7 +8814,6 @@
       <c r="F16" t="n">
         <v>15.58</v>
       </c>
-      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -10389,9 +8821,7 @@
           <t>VIX</t>
         </is>
       </c>
-      <c r="B17" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B17" s="10" t="n"/>
       <c r="C17" s="5" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -10418,9 +8848,7 @@
           <t>ZS</t>
         </is>
       </c>
-      <c r="B18" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B18" s="17" t="n"/>
       <c r="C18" s="16" t="inlineStr">
         <is>
           <t>12 网络安全</t>
@@ -10582,9 +9010,7 @@
           <t>ASTS</t>
         </is>
       </c>
-      <c r="B30" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B30" s="10" t="n"/>
       <c r="C30" s="5" t="inlineStr">
         <is>
           <t>17 高弹性交易池</t>
@@ -10611,9 +9037,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B31" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B31" s="10" t="n"/>
       <c r="C31" s="5" t="inlineStr">
         <is>
           <t>15 公用事业</t>
@@ -10640,9 +9064,7 @@
           <t>ENTG</t>
         </is>
       </c>
-      <c r="B32" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B32" s="10" t="n"/>
       <c r="C32" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -10669,9 +9091,7 @@
           <t>META</t>
         </is>
       </c>
-      <c r="B33" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B33" s="10" t="n"/>
       <c r="C33" s="5" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -10698,9 +9118,7 @@
           <t>NVTS</t>
         </is>
       </c>
-      <c r="B34" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B34" s="10" t="n"/>
       <c r="C34" s="5" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -10727,9 +9145,7 @@
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B35" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B35" s="10" t="n"/>
       <c r="C35" s="5" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -10840,7 +9256,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12004,8 +10419,6 @@
       <c r="T13" t="b">
         <v>0</v>
       </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>4H 0出; 4H_RSI=46.98; 4H分金=54.88</t>
@@ -12435,8 +10848,6 @@
       <c r="T18" t="b">
         <v>0</v>
       </c>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
           <t>4H 0出; 4H_RSI=49.02; 4H分金=55.10</t>
@@ -13081,7 +11492,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -13475,8 +11886,6 @@
       <c r="T30" t="b">
         <v>0</v>
       </c>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
         <is>
           <t>4H 0出; 4H_RSI=39.36; 4H分金=37.70</t>
@@ -13993,8 +12402,6 @@
       <c r="T36" t="b">
         <v>0</v>
       </c>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
         <is>
           <t>4H 0出; 4H_RSI=44.86; 4H分金=51.19</t>
@@ -15468,8 +13875,6 @@
       <c r="T53" t="b">
         <v>0</v>
       </c>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr">
         <is>
           <t>4H 0出; 4H_RSI=40.25; 4H分金=32.84</t>
@@ -15551,8 +13956,6 @@
       <c r="T54" t="b">
         <v>0</v>
       </c>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr">
         <is>
           <t>4H 0出; 4H_RSI=46.15; 4H分金=54.64</t>
@@ -16059,7 +14462,6 @@
       <c r="D2" s="8" t="n">
         <v>46170</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" s="8" t="n">
         <v>46170</v>
       </c>
@@ -16108,7 +14510,6 @@
           <t>98 超巨</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" s="8" t="n">
         <v>46168</v>
       </c>
@@ -16163,7 +14564,6 @@
       <c r="D4" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" s="8" t="n">
         <v>46164</v>
       </c>
@@ -16269,7 +14669,6 @@
       <c r="D6" s="8" t="n">
         <v>46170</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" s="8" t="n">
         <v>46170</v>
       </c>
@@ -16928,7 +15327,6 @@
       <c r="I9" t="n">
         <v>2</v>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" s="8" t="n">
         <v>46171</v>
       </c>
@@ -17040,7 +15438,6 @@
       <c r="I11" t="n">
         <v>4</v>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" s="8" t="n">
         <v>46169</v>
       </c>
@@ -17129,7 +15526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -17251,9 +15648,7 @@
           <t>AAOI</t>
         </is>
       </c>
-      <c r="B3" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B3" s="10" t="n"/>
       <c r="C3" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -17314,9 +15709,7 @@
           <t>BWXT</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B4" s="10" t="n"/>
       <c r="C4" s="5" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -17377,9 +15770,7 @@
           <t>CAMT</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B5" s="10" t="n"/>
       <c r="C5" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -17440,9 +15831,7 @@
           <t>COHU</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B6" s="10" t="n"/>
       <c r="C6" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -17499,9 +15888,7 @@
           <t>CPNG</t>
         </is>
       </c>
-      <c r="B7" s="13" t="n">
-        <v/>
-      </c>
+      <c r="B7" s="13" t="n"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>23 杂项</t>
@@ -17562,9 +15949,7 @@
           <t>CRM</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B8" s="17" t="n"/>
       <c r="C8" s="16" t="inlineStr">
         <is>
           <t>11 AI软件 / SAAS</t>
@@ -17625,9 +16010,7 @@
           <t>DD</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B9" s="10" t="n"/>
       <c r="C9" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -17688,9 +16071,7 @@
           <t>EOG</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n">
-        <v/>
-      </c>
+      <c r="B10" s="13" t="n"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -17751,9 +16132,7 @@
           <t>ETN</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B11" s="10" t="n"/>
       <c r="C11" s="5" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -17814,9 +16193,7 @@
           <t>GEV</t>
         </is>
       </c>
-      <c r="B12" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B12" s="10" t="n"/>
       <c r="C12" s="5" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -17877,9 +16254,7 @@
           <t>LEU</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B13" s="10" t="n"/>
       <c r="C13" s="5" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -17940,9 +16315,7 @@
           <t>MDB</t>
         </is>
       </c>
-      <c r="B14" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B14" s="10" t="n"/>
       <c r="C14" s="5" t="inlineStr">
         <is>
           <t>11 AI软件 / SAAS</t>
@@ -18003,9 +16376,7 @@
           <t>MOS</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n">
-        <v/>
-      </c>
+      <c r="B15" s="13" t="n"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>18 化肥</t>
@@ -18066,9 +16437,7 @@
           <t>NUE</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n">
-        <v/>
-      </c>
+      <c r="B16" s="13" t="n"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>13 材料 / 电网</t>
@@ -18117,7 +16486,6 @@
       <c r="P16" s="15" t="n">
         <v>0.084009</v>
       </c>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
@@ -18125,9 +16493,7 @@
           <t>NXT</t>
         </is>
       </c>
-      <c r="B17" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B17" s="17" t="n"/>
       <c r="C17" s="16" t="inlineStr">
         <is>
           <t>10 太阳能</t>
@@ -18184,9 +16550,7 @@
           <t>ONTO</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B18" s="10" t="n"/>
       <c r="C18" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -18247,9 +16611,7 @@
           <t>TEAM</t>
         </is>
       </c>
-      <c r="B19" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B19" s="17" t="n"/>
       <c r="C19" s="16" t="inlineStr">
         <is>
           <t>11 AI软件 / SAAS</t>
@@ -18310,9 +16672,7 @@
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B20" s="13" t="n">
-        <v/>
-      </c>
+      <c r="B20" s="13" t="n"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -18361,7 +16721,6 @@
       <c r="P20" s="14" t="n">
         <v>-0.023779</v>
       </c>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -18369,9 +16728,7 @@
           <t>UEC</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B21" s="10" t="n"/>
       <c r="C21" s="5" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -18617,9 +16974,7 @@
           <t>HAL</t>
         </is>
       </c>
-      <c r="B33" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B33" s="10" t="n"/>
       <c r="C33" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -18708,11 +17063,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18724,7 +17074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -18885,24 +17235,12 @@
       <c r="J3" s="5" t="n">
         <v>181.49</v>
       </c>
-      <c r="K3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P3" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K3" s="5" t="n"/>
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
+      <c r="P3" s="5" t="n"/>
       <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -18954,24 +17292,12 @@
       <c r="J4" s="5" t="n">
         <v>202.91</v>
       </c>
-      <c r="K4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P4" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="5" t="n"/>
       <c r="Q4" s="5" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19023,24 +17349,12 @@
       <c r="J5" s="5" t="n">
         <v>167.37</v>
       </c>
-      <c r="K5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
       <c r="Q5" s="5" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19092,24 +17406,12 @@
       <c r="J6" s="5" t="n">
         <v>46.53</v>
       </c>
-      <c r="K6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
       <c r="Q6" s="5" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19161,24 +17463,6 @@
       <c r="J7" t="n">
         <v>16.12</v>
       </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19230,24 +17514,12 @@
       <c r="J8" s="5" t="n">
         <v>180.07</v>
       </c>
-      <c r="K8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P8" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
       <c r="Q8" s="5" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19299,24 +17571,12 @@
       <c r="J9" s="5" t="n">
         <v>48.12</v>
       </c>
-      <c r="K9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P9" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="5" t="n"/>
       <c r="Q9" s="5" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19368,24 +17628,6 @@
       <c r="J10" t="n">
         <v>141.22</v>
       </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19437,24 +17679,12 @@
       <c r="J11" s="5" t="n">
         <v>391.35</v>
       </c>
-      <c r="K11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P11" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+      <c r="P11" s="5" t="n"/>
       <c r="Q11" s="5" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19506,24 +17736,12 @@
       <c r="J12" s="5" t="n">
         <v>1038.74</v>
       </c>
-      <c r="K12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+      <c r="P12" s="5" t="n"/>
       <c r="Q12" s="5" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19575,24 +17793,12 @@
       <c r="J13" s="5" t="n">
         <v>179.36</v>
       </c>
-      <c r="K13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P13" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="5" t="n"/>
       <c r="Q13" s="5" t="inlineStr">
         <is>
           <t>D0=179.36; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19644,24 +17850,12 @@
       <c r="J14" s="5" t="n">
         <v>326.13</v>
       </c>
-      <c r="K14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="5" t="n"/>
       <c r="Q14" s="5" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19713,24 +17907,6 @@
       <c r="J15" t="n">
         <v>22.51</v>
       </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>D0=22.51; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19782,24 +17958,6 @@
       <c r="J16" t="n">
         <v>232</v>
       </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19851,24 +18009,6 @@
       <c r="J17" t="n">
         <v>130.5</v>
       </c>
-      <c r="K17" t="n">
-        <v/>
-      </c>
-      <c r="L17" t="n">
-        <v/>
-      </c>
-      <c r="M17" t="n">
-        <v/>
-      </c>
-      <c r="N17" t="n">
-        <v/>
-      </c>
-      <c r="O17" t="n">
-        <v/>
-      </c>
-      <c r="P17" t="n">
-        <v/>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19920,24 +18060,12 @@
       <c r="J18" s="5" t="n">
         <v>262.25</v>
       </c>
-      <c r="K18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P18" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+      <c r="P18" s="5" t="n"/>
       <c r="Q18" s="5" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19989,24 +18117,12 @@
       <c r="J19" s="5" t="n">
         <v>85.42</v>
       </c>
-      <c r="K19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P19" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+      <c r="P19" s="5" t="n"/>
       <c r="Q19" s="5" t="inlineStr">
         <is>
           <t>D0=85.42; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20058,24 +18174,6 @@
       <c r="J20" t="n">
         <v>426.01</v>
       </c>
-      <c r="K20" t="n">
-        <v/>
-      </c>
-      <c r="L20" t="n">
-        <v/>
-      </c>
-      <c r="M20" t="n">
-        <v/>
-      </c>
-      <c r="N20" t="n">
-        <v/>
-      </c>
-      <c r="O20" t="n">
-        <v/>
-      </c>
-      <c r="P20" t="n">
-        <v/>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20127,24 +18225,12 @@
       <c r="J21" s="5" t="n">
         <v>13.02</v>
       </c>
-      <c r="K21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P21" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="5" t="n"/>
       <c r="Q21" s="5" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20381,24 +18467,12 @@
       <c r="J33" s="5" t="n">
         <v>41.47</v>
       </c>
-      <c r="K33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P33" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="n"/>
+      <c r="O33" s="5" t="n"/>
+      <c r="P33" s="5" t="n"/>
       <c r="Q33" s="5" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20443,11 +18517,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20459,7 +18528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O44"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -20569,9 +18638,7 @@
           <t>AMKR</t>
         </is>
       </c>
-      <c r="B3" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B3" s="17" t="n"/>
       <c r="C3" s="16" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -20626,9 +18693,7 @@
           <t>AVGO</t>
         </is>
       </c>
-      <c r="B4" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B4" s="17" t="n"/>
       <c r="C4" s="16" t="inlineStr">
         <is>
           <t>03 GPU / AI芯片</t>
@@ -20679,9 +18744,7 @@
           <t>BHP</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B5" s="10" t="n"/>
       <c r="C5" s="5" t="inlineStr">
         <is>
           <t>13 材料 / 电网</t>
@@ -20732,9 +18795,7 @@
           <t>CCJ</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B6" s="10" t="n"/>
       <c r="C6" s="5" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -20789,9 +18850,7 @@
           <t>CRWV</t>
         </is>
       </c>
-      <c r="B7" s="13" t="n">
-        <v/>
-      </c>
+      <c r="B7" s="13" t="n"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>21 数据中心</t>
@@ -20846,9 +18905,7 @@
           <t>GDX</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B8" s="17" t="n"/>
       <c r="C8" s="16" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -20903,9 +18960,7 @@
           <t>GDXU</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B9" s="10" t="n"/>
       <c r="C9" s="5" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -20960,9 +19015,7 @@
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B10" s="17" t="n"/>
       <c r="C10" s="16" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -21017,9 +19070,7 @@
           <t>META</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B11" s="10" t="n"/>
       <c r="C11" s="5" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -21070,9 +19121,7 @@
           <t>OKLO</t>
         </is>
       </c>
-      <c r="B12" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B12" s="10" t="n"/>
       <c r="C12" s="5" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -21085,7 +19134,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>买入跟踪 | 第一买入点</t>
+          <t>买入跟踪 | 第一观察点</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
@@ -21127,9 +19176,7 @@
           <t>RIO</t>
         </is>
       </c>
-      <c r="B13" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B13" s="17" t="n"/>
       <c r="C13" s="16" t="inlineStr">
         <is>
           <t>13 材料 / 电网</t>
@@ -21180,9 +19227,7 @@
           <t>SMR</t>
         </is>
       </c>
-      <c r="B14" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B14" s="10" t="n"/>
       <c r="C14" s="5" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -21195,7 +19240,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>买入跟踪 | 第一买入点</t>
+          <t>买入跟踪 | 第一观察点</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
@@ -21233,9 +19278,7 @@
           <t>SOLS</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B15" s="17" t="n"/>
       <c r="C15" s="16" t="inlineStr">
         <is>
           <t>17 高弹性交易池</t>
@@ -21286,9 +19329,7 @@
           <t>UUUU</t>
         </is>
       </c>
-      <c r="B16" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B16" s="10" t="n"/>
       <c r="C16" s="5" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -21343,9 +19384,7 @@
           <t>VRT</t>
         </is>
       </c>
-      <c r="B17" s="17" t="n">
-        <v/>
-      </c>
+      <c r="B17" s="17" t="n"/>
       <c r="C17" s="16" t="inlineStr">
         <is>
           <t>06 服务器 / 数据中心硬件</t>
@@ -21575,9 +19614,7 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="B29" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B29" s="10" t="n"/>
       <c r="C29" s="5" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -21628,9 +19665,7 @@
           <t>CVX</t>
         </is>
       </c>
-      <c r="B30" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B30" s="10" t="n"/>
       <c r="C30" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -21681,9 +19716,7 @@
           <t>EOG</t>
         </is>
       </c>
-      <c r="B31" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B31" s="10" t="n"/>
       <c r="C31" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -21734,9 +19767,7 @@
           <t>GDXD</t>
         </is>
       </c>
-      <c r="B32" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B32" s="10" t="n"/>
       <c r="C32" s="5" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -21787,9 +19818,7 @@
           <t>MDB</t>
         </is>
       </c>
-      <c r="B33" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B33" s="10" t="n"/>
       <c r="C33" s="5" t="inlineStr">
         <is>
           <t>11 AI软件 / SAAS</t>
@@ -21840,9 +19869,7 @@
           <t>OXY</t>
         </is>
       </c>
-      <c r="B34" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B34" s="10" t="n"/>
       <c r="C34" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -21893,9 +19920,7 @@
           <t>POET</t>
         </is>
       </c>
-      <c r="B35" s="10" t="n">
-        <v/>
-      </c>
+      <c r="B35" s="10" t="n"/>
       <c r="C35" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -22017,8 +20042,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43"/>
-    <row r="44"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
